--- a/output/2021/sector_totals_2021.xlsx
+++ b/output/2021/sector_totals_2021.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1956.332479084891</v>
+        <v>1956.332475398304</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>743.3541054387064</v>
+        <v>734.4207155568544</v>
       </c>
       <c r="E3" t="n">
-        <v>431.7541254269601</v>
+        <v>432.9831360393758</v>
       </c>
       <c r="F3" t="n">
-        <v>87.36921944896264</v>
+        <v>88.28735326677602</v>
       </c>
       <c r="G3" t="n">
-        <v>4.507546593314935</v>
+        <v>4.473497762033726</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6353.449937533635</v>
+        <v>6353.449933847049</v>
       </c>
       <c r="C16" t="n">
         <v>542.9364197255203</v>
       </c>
       <c r="D16" t="n">
-        <v>4921.194835501061</v>
+        <v>4912.26144561921</v>
       </c>
       <c r="E16" t="n">
-        <v>7089.368253499344</v>
+        <v>7090.59726411176</v>
       </c>
       <c r="F16" t="n">
-        <v>1576.415905663841</v>
+        <v>1577.334039481655</v>
       </c>
       <c r="G16" t="n">
-        <v>36.44984764379367</v>
+        <v>36.41579881251246</v>
       </c>
     </row>
   </sheetData>

--- a/output/2021/sector_totals_2021.xlsx
+++ b/output/2021/sector_totals_2021.xlsx
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1956.332475398304</v>
+        <v>2075.374544984077</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>734.4207155568544</v>
+        <v>820.029271408103</v>
       </c>
       <c r="E3" t="n">
-        <v>432.9831360393758</v>
+        <v>2325.796473184448</v>
       </c>
       <c r="F3" t="n">
-        <v>88.28735326677602</v>
+        <v>207.1554421881564</v>
       </c>
       <c r="G3" t="n">
-        <v>4.473497762033726</v>
+        <v>90.82355738085974</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6353.449933847049</v>
+        <v>6472.492003432821</v>
       </c>
       <c r="C16" t="n">
         <v>542.9364197255203</v>
       </c>
       <c r="D16" t="n">
-        <v>4912.26144561921</v>
+        <v>4997.870001470457</v>
       </c>
       <c r="E16" t="n">
-        <v>7090.59726411176</v>
+        <v>8983.410601256834</v>
       </c>
       <c r="F16" t="n">
-        <v>1577.334039481655</v>
+        <v>1696.202128403035</v>
       </c>
       <c r="G16" t="n">
-        <v>36.41579881251246</v>
+        <v>122.7658584313385</v>
       </c>
     </row>
   </sheetData>

--- a/output/2021/sector_totals_2021.xlsx
+++ b/output/2021/sector_totals_2021.xlsx
@@ -492,10 +492,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2075.374544984077</v>
+        <v>1953.592429974953</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>121.7821150091234</v>
       </c>
       <c r="D3" t="n">
         <v>820.029271408103</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6472.492003432821</v>
+        <v>6350.709888423698</v>
       </c>
       <c r="C16" t="n">
-        <v>542.9364197255203</v>
+        <v>664.7185347346438</v>
       </c>
       <c r="D16" t="n">
         <v>4997.870001470457</v>

--- a/output/2021/sector_totals_2021.xlsx
+++ b/output/2021/sector_totals_2021.xlsx
@@ -470,7 +470,7 @@
         <v>2651.9</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>345.03</v>
       </c>
       <c r="D2" t="n">
         <v>1520.7</v>
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1953.592429974953</v>
+        <v>2085.983466972077</v>
       </c>
       <c r="C3" t="n">
-        <v>121.7821150091234</v>
+        <v>132.3910369971231</v>
       </c>
       <c r="D3" t="n">
-        <v>820.029271408103</v>
+        <v>827.4470085647672</v>
       </c>
       <c r="E3" t="n">
-        <v>2325.796473184448</v>
+        <v>2490.697501435906</v>
       </c>
       <c r="F3" t="n">
-        <v>207.1554421881564</v>
+        <v>217.6520760616148</v>
       </c>
       <c r="G3" t="n">
-        <v>90.82355738085974</v>
+        <v>98.34572965742019</v>
       </c>
     </row>
     <row r="4">
@@ -817,22 +817,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6350.709888423698</v>
+        <v>6483.10092542082</v>
       </c>
       <c r="C16" t="n">
-        <v>664.7185347346438</v>
+        <v>1020.357456722644</v>
       </c>
       <c r="D16" t="n">
-        <v>4997.870001470457</v>
+        <v>5005.287738627121</v>
       </c>
       <c r="E16" t="n">
-        <v>8983.410601256834</v>
+        <v>9148.311629508291</v>
       </c>
       <c r="F16" t="n">
-        <v>1696.202128403035</v>
+        <v>1706.698762276493</v>
       </c>
       <c r="G16" t="n">
-        <v>122.7658584313385</v>
+        <v>130.2880307078989</v>
       </c>
     </row>
   </sheetData>
